--- a/output/PIB_UPSC_Daily_2026-10-13.xlsx
+++ b/output/PIB_UPSC_Daily_2026-10-13.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,11 +34,15 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <b val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="002563EB"/>
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -53,12 +57,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00334155"/>
         <bgColor rgb="00334155"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -66,19 +88,51 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -493,7 +547,768 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Prime Minister's Office</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Former UK Prime Minister Rishi Sunak meets Prime Minister Shri Narendra Modi at Bloomberg New Economy Forum</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Aligned with General Studies 3 topics: economy</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2323023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Prime Minister's Office</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Prime Minister Shri Narendra Modi addresses the Bloomberg New Economy Forum</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Aligned with General Studies 3 topics: economy</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322664</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Prime Minister's Office</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>English rendering of PM’s address at the Bloomberg New Economy Forum in New Delhi</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Aligned with General Studies 3 topics: economy</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322622</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture &amp;
+Farmers Welfare</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Union Agriculture Minister Shri Shivraj Singh Chouhan and Environment Minister Shri Bhupender Yadav conduct joint review of stubble management</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>agriculture</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Aligned with General Studies 3 topics: agriculture</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322991</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture &amp;
+Farmers Welfare</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>10th National Convention of Agrivision–2026 held in New Delhi</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>agriculture</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Aligned with General Studies 3 topics: agriculture</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322911</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture &amp;
+Farmers Welfare</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Improved Soybean Varieties NRC 268 and NRC 270 Show Promising Signs of Yielding 20 Quintals per Hectare Despite Adverse Weather Conditions</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>agriculture</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Aligned with General Studies 3 topics: agriculture</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322744</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Commerce &amp; Industry</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>PM GatiShakti National Master Plan completes five years of transforming India’s infrastructure landscape</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>infrastructure</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Aligned with General Studies 3 topics: infrastructure</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322825</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>GS-1</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Culture</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Hindustan Aeronautics Limited (HAL), National Culture Fund (NCF) and Archaeological Survey of India (ASI) Sign MoA for Conservation and Development of Heritage Sites</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>heritage</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Aligned with General Studies 1 topics: heritage</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322976</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Defence</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>DRDO to lead thematic session on ‘Semiconductors &amp; Next-Gen Chips’ at ESTIC-2026</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>drdo</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Aligned with General Studies 3 topics: drdo</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322945</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Defence</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>INDIAN NAVY SET TO COMMISSION INDIGENOUS MULTI PURPOSE WARSHIP SAMARTHAK</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>indian navy</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Aligned with General Studies 3 topics: indian navy</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322795</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Environment, Forest and Climate Change</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Union Environment Minister and CM (NCT Delhi) review Air Pollution Mitigation measures at Anand Vihar Hotspot and visit DPCC’s AI-enabled ICCC facility at Shastri Park</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>climate change</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Aligned with General Studies 3 topics: climate change</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322719</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>GS-2</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Fisheries, Animal Husbandry &amp; Dairying</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Union Minister Shri Rajiv Ranjan Singh alias Lalan Singh Launches DBIM-Compliant DAHD Website to Strengthen Digital Governance</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>governance</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Aligned with General Studies 2 topics: governance</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322814</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Fisheries, Animal Husbandry &amp; Dairying</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Union Fisheries Secretary Dr. Abhilaksh Likhi Visits Mandapam Seaweed Cultivation Site; Interacts with Seaweed Farmers, Self-Help Groups and Scientists</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>animal husbandry</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Aligned with General Studies 3 topics: animal husbandry</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322786</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Food Processing Industries</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>NIFTEM-K Hosts India–Canada Roundtable on Pulse Protein Innovation, Value Addition and Strategic Partnerships</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>food processing</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Aligned with General Studies 3 topics: food processing</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322955</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>GS-2</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Heavy Industries</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Hon’ble Chairperson National Commission for Scheduled Tribes (NCST) Shri Antar Singh Arya reviewed the implementation of constitutionals safeguards and various programmes for ST’s by Ministry of Heavy Industries</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>scheduled tribes</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Aligned with General Studies 2 topics: scheduled tribes</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322808</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>GS-2</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Law and Justice</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>President Appoints Two Judicial Officers as Additional Judges of Madras High Court</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>high court</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Aligned with General Studies 2 topics: high court</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322855</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>GS-2</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Personnel, Public Grievances &amp; Pensions</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>DARPG releases the 53rd Monthly Report on Centralized Public Grievance Redress and Monitoring System (CPGRAMS) for Central Ministries/ Departments performance for the month of September, 2026</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Administrative Reforms &amp; Governance Quality</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Strategic policy update from nodal ministry (Ministry of Personnel, Public Grievances &amp; Pensions): Administrative Reforms &amp; Governance Quality</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322665</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>GS-2</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Personnel, Public Grievances &amp; Pensions</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>DARPG releases the 50th Report on Centralized Public Grievance Redress and Monitoring System (CPGRAMS) for States/UTs for September, 2026</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Administrative Reforms &amp; Governance Quality</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Strategic policy update from nodal ministry (Ministry of Personnel, Public Grievances &amp; Pensions): Administrative Reforms &amp; Governance Quality</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322663</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Road Transport &amp; Highways</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>From Farms to Borders: NH-22 Four-Laning Project to Boost Connectivity and Economic Growth in Bihar</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>economic growth</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Aligned with General Studies 3 topics: economic growth</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322801</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>GS-1</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Preserving Himalayas a National Responsibility; Every Citizen Has a Stake: Dr Jitendra Singh</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Aligned with General Studies 1 topics: himalayas</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322833</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>GS-1</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Tribal Affairs</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Tribal Affairs and Karmayogi Bharat sign MoU to bring the iGOT Karmayogi learning platform to Adi Karmayogi Volunteers</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>tribal</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Aligned with General Studies 1 topics: tribal</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322927</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -504,7 +1319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -516,32 +1331,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>S.No.</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Classification</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Paper</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Headline</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>PIB URL</t>
         </is>
@@ -563,23 +1378,1886 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>President's Secretariat</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PRESIDENT OF INDIA TO GRACE THE NATIONAL SARAS MELA IN VIJAYAWADA</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322953</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>President's Secretariat</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FACULTY AND COURSE MEMBERS OF 66TH NATIONAL DEFENCE COLLEGE COURSE CALL ON THE PRESIDENT</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322784</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Prime Minister's Office</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Prime Minister holds warm and productive conversation with Canadian Prime Minister Mark Carney, discusses strengthening Strategic Partnership</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2323025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Relevant (UPSC)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Prime Minister's Office</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Former UK Prime Minister Rishi Sunak meets Prime Minister Shri Narendra Modi at Bloomberg New Economy Forum</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2323023</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Routine/Ceremonial</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Prime Minister's Office</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Prime Minister welcomes Bloomberg’s plans to expand presence in India</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2323020</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Relevant (UPSC)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Prime Minister's Office</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Prime Minister Shri Narendra Modi addresses the Bloomberg New Economy Forum</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322664</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Relevant (UPSC)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Prime Minister's Office</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>English rendering of PM’s address at the Bloomberg New Economy Forum in New Delhi</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322622</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Prime Minister's Office</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Prime Minister offers prayers to Maa Chandraghanta during Navratri</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322599</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Routine/Ceremonial</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Prime Minister's Office</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Prime Minister shares Sanskrit Subhashitam highlighting the divine power and grace of the Goddess</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322597</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AYUSH</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ayush Ministry Releases Treatment Guidelines for Skin Disorders Across Four Traditional Systems</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322793</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Relevant (UPSC)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture &amp;
+Farmers Welfare</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Union Agriculture Minister Shri Shivraj Singh Chouhan and Environment Minister Shri Bhupender Yadav conduct joint review of stubble management</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322991</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Relevant (UPSC)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture &amp;
+Farmers Welfare</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>10th National Convention of Agrivision–2026 held in New Delhi</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322911</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Relevant (UPSC)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture &amp;
+Farmers Welfare</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Improved Soybean Varieties NRC 268 and NRC 270 Show Promising Signs of Yielding 20 Quintals per Hectare Despite Adverse Weather Conditions</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322744</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ministry of Coal</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>MCL strengthens E-Waste Management Across Its Establishments under Special Campaign 6</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322767</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Relevant (UPSC)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ministry of Commerce &amp; Industry</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PM GatiShakti National Master Plan completes five years of transforming India’s infrastructure landscape</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322825</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ministry of Communications</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>India Post and IndiGo take postcards to the skies with Digital Detox Campaign</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322766</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Relevant (UPSC)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GS-1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Ministry of Culture</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Hindustan Aeronautics Limited (HAL), National Culture Fund (NCF) and Archaeological Survey of India (ASI) Sign MoA for Conservation and Development of Heritage Sites</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322976</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Routine/Ceremonial</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ministry of Culture</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Celebrating Uttarakhand’s Spiritual Heritage at the 8th edition of PM Mementos e-Auction</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322678</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Relevant (UPSC)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Ministry of Defence</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>DRDO to lead thematic session on ‘Semiconductors &amp; Next-Gen Chips’ at ESTIC-2026</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322945</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Relevant (UPSC)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Ministry of Defence</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>INDIAN NAVY SET TO COMMISSION INDIGENOUS MULTI PURPOSE WARSHIP SAMARTHAK</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322795</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Ministry of Defence</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RRM to Attend Special Joint State Representatives and Additional Director General’s Conference 2026 of NCC in Guwahati</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322772</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ministry of Defence</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Raksha Mantri holds bilateral talks with 1st Deputy Prime Minister and Minister of Industry &amp; Trade of Czech Republic</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322692</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>Ministry of Development of North-East Region</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Union Minister Jyotiraditya Scindia Inaugurates North East Bankers’ Conclave 3.0 in Mizoram, Calls for Greater Credit Flow to Region</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2323021</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Ministry of Development of North-East Region</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>Union Minister Jyotiraditya M. Scindia Interacts with Students at Mizoram University</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322586</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Ministry of Education</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ministry of Education, constitutes Three Member Committee to examine student death at IIIT, Ranchi</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322729</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Ministry of Electronics &amp; IT</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Taking Voice-First Multilingual AI Beyond Borders: BHASHINI at NCGG Mussoorie</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322621</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Relevant (UPSC)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Ministry of Environment, Forest and Climate Change</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Union Environment Minister and CM (NCT Delhi) review Air Pollution Mitigation measures at Anand Vihar Hotspot and visit DPCC’s AI-enabled ICCC facility at Shastri Park</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322719</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Relevant (UPSC)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>GS-2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Ministry of Fisheries, Animal Husbandry &amp; Dairying</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Union Minister Shri Rajiv Ranjan Singh alias Lalan Singh Launches DBIM-Compliant DAHD Website to Strengthen Digital Governance</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322814</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Relevant (UPSC)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Ministry of Fisheries, Animal Husbandry &amp; Dairying</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Union Fisheries Secretary Dr. Abhilaksh Likhi Visits Mandapam Seaweed Cultivation Site; Interacts with Seaweed Farmers, Self-Help Groups and Scientists</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322786</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Ministry of Finance</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>NLMC’s first end-to-end e-auction of RINL land parcels generates ₹366.33 Crore in successful bids on Day 1, 150 plots sold</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322696</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Relevant (UPSC)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Ministry of Food Processing Industries</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>NIFTEM-K Hosts India–Canada Roundtable on Pulse Protein Innovation, Value Addition and Strategic Partnerships</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322955</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Ministry of Heavy Industries</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ministry of Heavy Industries and its Central Public Sector Enterprises (CPSEs) &amp; Autonomous Bodies(ABs) observes Special Campaign 6</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322919</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Relevant (UPSC)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>GS-2</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Ministry of Heavy Industries</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Hon’ble Chairperson National Commission for Scheduled Tribes (NCST) Shri Antar Singh Arya reviewed the implementation of constitutionals safeguards and various programmes for ST’s by Ministry of Heavy Industries</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322808</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Ministry of Home Affairs</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>First BIMSTEC Home Ministers’ Meeting concludes with adoption of Delhi Declaration</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322964</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Ministry of Home Affairs</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Under the chairmanship of Union Home Minister Shri Amit Shah, India hosts first meeting of BIMSTEC Home Ministers in New Delhi</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322937</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Ministry of Jal Shakti</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Industrial Pollution Abatement: Sustainability through Regulations under Namami Gange</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322666</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Ministry of Labour &amp; Employment</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Retrospective regularization of exempt status of Provident Fund (PF) Trusts through Amnesty Scheme, 2026</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322732</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Ministry of Law and Justice</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Legislative Department Organises Workshop on Record Management under Special Campaign 6.</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322999</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Relevant (UPSC)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>GS-2</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Ministry of Law and Justice</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>President Appoints Two Judicial Officers as Additional Judges of Madras High Court</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322855</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Ministry of Mines</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Ministry of Mines Organises Outreach Programme on Auction of Offshore Mineral Blocks</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322967</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Ministry of Panchayati Raj</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Ministry of Panchayati Raj to undertake cleanliness drive and disposal of pending matters on 14 October 2026 under Special Campaign 6.0</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322921</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Relevant (UPSC)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>GS-2</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Ministry of Personnel, Public Grievances &amp; Pensions</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>DARPG releases the 53rd Monthly Report on Centralized Public Grievance Redress and Monitoring System (CPGRAMS) for Central Ministries/ Departments performance for the month of September, 2026</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322665</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Relevant (UPSC)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>GS-2</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Ministry of Personnel, Public Grievances &amp; Pensions</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>DARPG releases the 50th Report on Centralized Public Grievance Redress and Monitoring System (CPGRAMS) for States/UTs for September, 2026</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322663</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Ministry of Power</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>CEA Brainstorming Event: Making Indian Power Sector AI Enabled</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322905</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Ministry of Railways</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Indian Railways Registers 6.14% Growth in Freight Loading in September 2026 over September 2025</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322673</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Relevant (UPSC)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>GS-3</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Ministry of Road Transport &amp; Highways</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>From Farms to Borders: NH-22 Four-Laning Project to Boost Connectivity and Economic Growth in Bihar</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322801</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Relevant (UPSC)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>GS-1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Ministry of Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Preserving Himalayas a National Responsibility; Every Citizen Has a Stake: Dr Jitendra Singh</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322833</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Ministry of Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>New technology provides environment friendly route for treating dye-contaminated wastewater</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322743</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Ministry of Ports, Shipping and Waterways</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>21st Meeting of Maritime State Development Council Concludes Successfully at Mumbai</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322942</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Ministry of Skill Development and Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>IndiaSkills 2026–27 Registration Window Reopened till 19 October Following Strong Demand from Aspirants</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322849</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Ministry of Social Justice &amp; Empowerment</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>From Financial Hardship to Research Aspirations</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322973</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Ministry of Social Justice &amp; Empowerment</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>From Limited Income to a More Secure Livelihood</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322968</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Ministry of Social Justice &amp; Empowerment</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>From Addiction to Self-Reliance: A Journey of Recovery and Renewed Hope</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322966</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Ministry of Social Justice &amp; Empowerment</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>NISD’s Five-Day Geriatric Caregivers Training Programme Successfully Concludes in Diu</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322949</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Ministry of Social Justice &amp; Empowerment</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Department of Social Justice And Empowerment Committed Towards Special Campaign 6</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322851</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Ministry of Statistics &amp; Programme Implementation</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Strong Statistical Systems Key to Achieving Viksit Bharat @ 2047: Dr. P. K. Mishra</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322662</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Relevant (UPSC)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>GS-1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Ministry of Tribal Affairs</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Ministry of Tribal Affairs and Karmayogi Bharat sign MoU to bring the iGOT Karmayogi learning platform to Adi Karmayogi Volunteers</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322927</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Ministry of Women and Child Development</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Union Women and Child Development Minister Smt. Annpurna Devi Visits NCPCR, Reviews Office Functioning and Directs Timely Disposal of Pending Files by December 31, 2026</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322938</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Ministry of Youth Affairs and Sports</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>NSDF, SAI Partner with Indian Oil to Strengthen Boxing Ecosystem in India</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322887</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>PIB Backgrounder</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Towards a TB-Free India</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322820</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Routine Fluff</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>General/Administrative</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>PIB Backgrounder</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Khadi &amp; Village Industries: From Tradition to Enterprise</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseDetail.aspx?PRID=2322625</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId61"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
